--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122344869</v>
       </c>
       <c r="B3" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -819,11 +819,6 @@
       <c r="E3" t="n">
         <v>100138</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122344869</v>
       </c>
       <c r="B3" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,6 +818,11 @@
       </c>
       <c r="E3" t="n">
         <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122344869</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74574145</v>
       </c>
       <c r="B2" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556224.3898702657</v>
+        <v>556224</v>
       </c>
       <c r="R2" t="n">
-        <v>6320927.700238621</v>
+        <v>6320928</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1988-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574145</v>
       </c>
       <c r="B2" t="n">
-        <v>109223</v>
+        <v>109232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574145</v>
       </c>
       <c r="B2" t="n">
-        <v>109232</v>
+        <v>109237</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574145</v>
       </c>
       <c r="B2" t="n">
-        <v>109237</v>
+        <v>109265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574145</v>
       </c>
       <c r="B2" t="n">
-        <v>109265</v>
+        <v>109271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574145</v>
       </c>
       <c r="B2" t="n">
-        <v>109271</v>
+        <v>109278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574145</v>
       </c>
       <c r="B2" t="n">
-        <v>109278</v>
+        <v>109282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574145</v>
       </c>
       <c r="B2" t="n">
-        <v>109282</v>
+        <v>109290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574145</v>
       </c>
       <c r="B2" t="n">
-        <v>109293</v>
+        <v>109298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574145</v>
       </c>
       <c r="B2" t="n">
-        <v>109298</v>
+        <v>109306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74574145</v>
       </c>
       <c r="B2" t="n">
-        <v>109306</v>
+        <v>109316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -675,48 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74574145</v>
+        <v>122344869</v>
       </c>
       <c r="B2" t="n">
-        <v>109316</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220228</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50 O Ramsgöl, Sm</t>
+          <t>Öst om Ransgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556224</v>
+        <v>556223</v>
       </c>
       <c r="R2" t="n">
-        <v>6320928</v>
+        <v>6320954</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1988-08-02</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1988-08-02</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5G4b 2423. SOM: Leontodon hispidus. LEG: John Christoffersson</t>
+          <t>Nära hygge.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,91 +776,67 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Torräng</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Albin Kozma</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
+          <t>Albin Kozma</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Smålands flora (1978-2007)</t>
+          <t>Fågelinventering Branthult 2024-2025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122344869</v>
+        <v>74574145</v>
       </c>
       <c r="B3" t="n">
-        <v>56594</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220228</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öst om Ransgöl, Sm</t>
+          <t>50 O Ramsgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556223</v>
+        <v>556224</v>
       </c>
       <c r="R3" t="n">
-        <v>6320954</v>
+        <v>6320928</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,17 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>1988-08-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>1988-08-02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Nära hygge.</t>
+          <t>Smålands flora 2007: KOO: 5G4b 2423. SOM: Leontodon hispidus. LEG: John Christoffersson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,20 +882,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Torräng</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Albin Kozma</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Albin Kozma</t>
+          <t>Via Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Fågelinventering Branthult 2024</t>
+          <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 33067-2022 artfynd.xlsx
+++ b/artfynd/A 33067-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Fågelinventering Branthult 2024-2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122344869</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,8 +913,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74574145</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>